--- a/output/stock_quant_scores/BABA_income_df.xlsx
+++ b/output/stock_quant_scores/BABA_income_df.xlsx
@@ -1386,7 +1386,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>80161000000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
@@ -1399,12 +1401,16 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>22.96</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>62249000000</v>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
@@ -1432,9 +1438,13 @@
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>313612000000</v>
+      </c>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>853062000000</v>
+      </c>
       <c r="BD6" t="inlineStr"/>
     </row>
   </sheetData>
